--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53282414-7544-4F7F-B775-9954824E3257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A084FA0-487E-4FD5-BFB7-01D7D28561F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="134">
   <si>
     <t>备注:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -511,6 +511,14 @@
   </si>
   <si>
     <t>螺旋突刺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只能对友军释放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -996,38 +1004,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AI69"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.453125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.26953125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="21.90625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="22.6328125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.25" style="2" customWidth="1"/>
+    <col min="11" max="11" width="21.875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="22.625" style="2" customWidth="1"/>
     <col min="13" max="13" width="17" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="255.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="255.625" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7265625" style="2" customWidth="1"/>
-    <col min="22" max="22" width="20.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.75" style="2" customWidth="1"/>
+    <col min="22" max="22" width="20.75" style="2" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="17" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="22" style="2" bestFit="1" customWidth="1"/>
     <col min="25" max="27" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="18.26953125" style="2" customWidth="1"/>
-    <col min="29" max="29" width="70.453125" style="2" customWidth="1"/>
+    <col min="28" max="28" width="18.25" style="2" customWidth="1"/>
+    <col min="29" max="29" width="70.5" style="2" customWidth="1"/>
     <col min="30" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="12" t="s">
         <v>9</v>
@@ -1103,7 +1111,7 @@
         <v>41</v>
       </c>
       <c r="AA1" s="12" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="AB1" s="12"/>
       <c r="AC1" s="6"/>
@@ -1114,7 +1122,7 @@
       <c r="AH1" s="8"/>
       <c r="AI1" s="6"/>
     </row>
-    <row r="2" spans="1:35" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1153,7 +1161,7 @@
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
     </row>
-    <row r="3" spans="1:35" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1242,7 +1250,7 @@
       <c r="AH3" s="7"/>
       <c r="AI3" s="7"/>
     </row>
-    <row r="4" spans="1:35" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1326,7 +1334,7 @@
       </c>
       <c r="AB4" s="15"/>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1392,7 +1400,7 @@
       <c r="AF5" s="4"/>
       <c r="AH5" s="4"/>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1459,7 +1467,7 @@
       <c r="AF6" s="4"/>
       <c r="AH6" s="4"/>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1533,7 +1541,7 @@
       <c r="AF7" s="4"/>
       <c r="AH7" s="4"/>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1604,7 +1612,7 @@
       <c r="AF8" s="4"/>
       <c r="AH8" s="4"/>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -1678,7 +1686,7 @@
       <c r="AF9" s="4"/>
       <c r="AH9" s="4"/>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -1749,7 +1757,7 @@
       <c r="AF10" s="4"/>
       <c r="AH10" s="4"/>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -1820,7 +1828,7 @@
       <c r="AF11" s="4"/>
       <c r="AH11" s="4"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -1891,7 +1899,7 @@
       <c r="AF12" s="4"/>
       <c r="AH12" s="4"/>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -1962,7 +1970,7 @@
       <c r="AF13" s="4"/>
       <c r="AH13" s="4"/>
     </row>
-    <row r="14" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2036,7 +2044,7 @@
       <c r="AF14" s="4"/>
       <c r="AH14" s="4"/>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2107,7 +2115,7 @@
       <c r="AF15" s="4"/>
       <c r="AH15" s="4"/>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2178,7 +2186,7 @@
       <c r="AF16" s="4"/>
       <c r="AH16" s="4"/>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2249,7 +2257,7 @@
       <c r="AF17" s="4"/>
       <c r="AH17" s="4"/>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2320,7 +2328,7 @@
       <c r="AF18" s="4"/>
       <c r="AH18" s="4"/>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2392,7 +2400,7 @@
       <c r="AF19" s="4"/>
       <c r="AH19" s="4"/>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -2461,7 +2469,7 @@
       <c r="AF20" s="4"/>
       <c r="AH20" s="4"/>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -2533,7 +2541,7 @@
       <c r="AF21" s="4"/>
       <c r="AH21" s="4"/>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -2605,7 +2613,7 @@
       <c r="AF22" s="4"/>
       <c r="AH22" s="4"/>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -2677,7 +2685,7 @@
       <c r="AF23" s="4"/>
       <c r="AH23" s="4"/>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -2694,7 +2702,7 @@
         <v>25</v>
       </c>
       <c r="G24" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H24" s="4">
         <v>15</v>
@@ -2749,7 +2757,7 @@
       <c r="AF24" s="4"/>
       <c r="AH24" s="4"/>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -2821,7 +2829,7 @@
       <c r="AF25" s="4"/>
       <c r="AH25" s="4"/>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -2891,7 +2899,7 @@
       <c r="AF26" s="4"/>
       <c r="AH26" s="4"/>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -2957,7 +2965,7 @@
       <c r="AF27" s="4"/>
       <c r="AH27" s="4"/>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>129</v>
       </c>
@@ -2989,8 +2997,8 @@
       <c r="K28" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="M28" s="4">
-        <v>2</v>
+      <c r="M28" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="N28" s="4">
         <v>0</v>
@@ -3028,7 +3036,7 @@
       <c r="AF28" s="4"/>
       <c r="AH28" s="4"/>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3057,8 +3065,8 @@
       <c r="K29" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="M29" s="4">
-        <v>2</v>
+      <c r="M29" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="N29" s="4">
         <v>0</v>
@@ -3097,7 +3105,7 @@
       <c r="AF29" s="4"/>
       <c r="AH29" s="4"/>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3124,8 +3132,8 @@
       <c r="K30" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="M30" s="4">
-        <v>2</v>
+      <c r="M30" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="N30" s="4">
         <v>0</v>
@@ -3164,7 +3172,7 @@
       <c r="AF30" s="4"/>
       <c r="AH30" s="4"/>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -3230,7 +3238,7 @@
       <c r="AF31" s="4"/>
       <c r="AH31" s="4"/>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.15">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -3296,7 +3304,7 @@
       <c r="AF32" s="4"/>
       <c r="AH32" s="4"/>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -3316,7 +3324,7 @@
       <c r="AF33" s="4"/>
       <c r="AH33" s="4"/>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -3336,7 +3344,7 @@
       <c r="AF34" s="4"/>
       <c r="AH34" s="4"/>
     </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -3356,7 +3364,7 @@
       <c r="AF35" s="4"/>
       <c r="AH35" s="4"/>
     </row>
-    <row r="36" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -3376,7 +3384,7 @@
       <c r="AF36" s="4"/>
       <c r="AH36" s="4"/>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -3396,7 +3404,7 @@
       <c r="AF37" s="4"/>
       <c r="AH37" s="4"/>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -3416,7 +3424,7 @@
       <c r="AF38" s="4"/>
       <c r="AH38" s="4"/>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3436,7 +3444,7 @@
       <c r="AF39" s="4"/>
       <c r="AH39" s="4"/>
     </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3455,7 +3463,7 @@
       <c r="AF40" s="4"/>
       <c r="AH40" s="4"/>
     </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3474,7 +3482,7 @@
       <c r="AF41" s="4"/>
       <c r="AH41" s="4"/>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -3493,7 +3501,7 @@
       <c r="AF42" s="4"/>
       <c r="AH42" s="4"/>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -3512,7 +3520,7 @@
       <c r="AF43" s="4"/>
       <c r="AH43" s="4"/>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -3531,7 +3539,7 @@
       <c r="AF44" s="4"/>
       <c r="AH44" s="4"/>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -3541,7 +3549,7 @@
       <c r="AF45" s="4"/>
       <c r="AH45" s="4"/>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -3550,139 +3558,139 @@
       <c r="AF46" s="4"/>
       <c r="AH46" s="4"/>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.15">
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.15">
       <c r="B69" s="4"/>
     </row>
   </sheetData>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A084FA0-487E-4FD5-BFB7-01D7D28561F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A8CDEB-F0AC-4472-9E97-71B000CF7AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="165">
   <si>
     <t>备注:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -519,6 +519,123 @@
   </si>
   <si>
     <t>1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>激活音效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>personSound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2810</t>
+  </si>
+  <si>
+    <t>2880,2894,2908</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2922</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2936</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2950</t>
+  </si>
+  <si>
+    <t>3062</t>
+  </si>
+  <si>
+    <t>2852</t>
+  </si>
+  <si>
+    <t>2824</t>
+  </si>
+  <si>
+    <t>2684</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2698,2684</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2880</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2824,3020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3048</t>
+  </si>
+  <si>
+    <t>2852,2964</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3020,3034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>actionSound</t>
+  </si>
+  <si>
+    <t>87</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>88</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>89</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>91</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>92</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>82</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>77</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>79</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>72</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>73</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>67</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -684,14 +801,14 @@
     <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1003,7 +1120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
-  <dimension ref="A1:AI69"/>
+  <dimension ref="A1:AJ69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.375" style="2" bestFit="1" customWidth="1"/>
@@ -1026,16 +1143,17 @@
     <col min="19" max="19" width="17" style="2" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16.625" style="2" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="19.75" style="2" customWidth="1"/>
-    <col min="22" max="22" width="20.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="18.25" style="2" customWidth="1"/>
-    <col min="29" max="29" width="70.5" style="2" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="2"/>
+    <col min="22" max="22" width="18.25" style="2" customWidth="1"/>
+    <col min="23" max="23" width="20.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.25" style="2" customWidth="1"/>
+    <col min="30" max="30" width="70.5" style="2" customWidth="1"/>
+    <col min="31" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="12" t="s">
         <v>9</v>
@@ -1089,40 +1207,43 @@
       <c r="S1" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="T1" s="16" t="s">
+      <c r="T1" s="15" t="s">
         <v>88</v>
       </c>
       <c r="U1" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="V1" s="16"/>
+      <c r="W1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="X1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="Y1" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="Y1" s="12" t="s">
-        <v>41</v>
       </c>
       <c r="Z1" s="12" t="s">
         <v>41</v>
       </c>
       <c r="AA1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB1" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="AB1" s="12"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="8"/>
-      <c r="AE1" s="6"/>
-      <c r="AF1" s="8"/>
-      <c r="AG1" s="6"/>
-      <c r="AH1" s="8"/>
-      <c r="AI1" s="6"/>
-    </row>
-    <row r="2" spans="1:35" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AC1" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="6"/>
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="6"/>
+    </row>
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1146,22 +1267,23 @@
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
+      <c r="V2" s="3"/>
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="2"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="3"/>
       <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
-    </row>
-    <row r="3" spans="1:35" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AJ2" s="2"/>
+    </row>
+    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1224,33 +1346,38 @@
         <v>46</v>
       </c>
       <c r="V3" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="W3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="X3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="Z3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AB3" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
+      <c r="AC3" s="7" t="s">
+        <v>135</v>
+      </c>
       <c r="AD3" s="7"/>
       <c r="AE3" s="7"/>
       <c r="AF3" s="7"/>
       <c r="AG3" s="7"/>
       <c r="AH3" s="7"/>
       <c r="AI3" s="7"/>
-    </row>
-    <row r="4" spans="1:35" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AJ3" s="7"/>
+    </row>
+    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1314,8 +1441,8 @@
       <c r="U4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="V4" s="13" t="s">
-        <v>8</v>
+      <c r="V4" s="14" t="s">
+        <v>65</v>
       </c>
       <c r="W4" s="13" t="s">
         <v>8</v>
@@ -1332,9 +1459,14 @@
       <c r="AA4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AB4" s="15"/>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AB4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC4" s="14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1377,7 +1509,7 @@
         <v>6</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>6</v>
@@ -1386,7 +1518,7 @@
         <v>6</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z5" s="2" t="s">
         <v>7</v>
@@ -1394,13 +1526,18 @@
       <c r="AA5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB5" s="4"/>
-      <c r="AD5" s="4"/>
+      <c r="AB5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
-      <c r="AH5" s="4"/>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AG5" s="4"/>
+      <c r="AI5" s="4"/>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1443,9 +1580,6 @@
       <c r="U6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="V6" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W6" s="2" t="s">
         <v>6</v>
       </c>
@@ -1453,7 +1587,7 @@
         <v>6</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>7</v>
@@ -1461,13 +1595,18 @@
       <c r="AA6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB6" s="4"/>
-      <c r="AD6" s="4"/>
+      <c r="AB6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
-      <c r="AH6" s="4"/>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AG6" s="4"/>
+      <c r="AI6" s="4"/>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1518,10 +1657,10 @@
         <v>6</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>7</v>
@@ -1535,13 +1674,18 @@
       <c r="AA7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB7" s="4"/>
-      <c r="AD7" s="4"/>
+      <c r="AB7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
-      <c r="AH7" s="4"/>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AG7" s="4"/>
+      <c r="AI7" s="4"/>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1589,10 +1733,10 @@
         <v>6</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8" s="2" t="s">
         <v>7</v>
@@ -1606,13 +1750,18 @@
       <c r="AA8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB8" s="4"/>
-      <c r="AD8" s="4"/>
+      <c r="AB8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>2838</v>
+      </c>
       <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
-      <c r="AH8" s="4"/>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AG8" s="4"/>
+      <c r="AI8" s="4"/>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -1663,10 +1812,10 @@
         <v>6</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9" s="2" t="s">
         <v>7</v>
@@ -1680,13 +1829,18 @@
       <c r="AA9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB9" s="4"/>
-      <c r="AD9" s="4"/>
+      <c r="AB9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
-      <c r="AH9" s="4"/>
-    </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AG9" s="4"/>
+      <c r="AI9" s="4"/>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -1734,10 +1888,10 @@
         <v>6</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>6</v>
+        <v>159</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X10" s="2" t="s">
         <v>7</v>
@@ -1751,13 +1905,18 @@
       <c r="AA10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB10" s="4"/>
-      <c r="AD10" s="4"/>
+      <c r="AB10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>2866</v>
+      </c>
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
-      <c r="AH10" s="4"/>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AG10" s="4"/>
+      <c r="AI10" s="4"/>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -1805,10 +1964,10 @@
         <v>6</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>6</v>
+        <v>160</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>7</v>
@@ -1822,13 +1981,18 @@
       <c r="AA11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB11" s="4"/>
-      <c r="AD11" s="4"/>
+      <c r="AB11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
-      <c r="AH11" s="4"/>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AG11" s="4"/>
+      <c r="AI11" s="4"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -1876,10 +2040,10 @@
         <v>6</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>7</v>
@@ -1893,13 +2057,18 @@
       <c r="AA12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB12" s="4"/>
-      <c r="AD12" s="4"/>
+      <c r="AB12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
-      <c r="AH12" s="4"/>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AG12" s="4"/>
+      <c r="AI12" s="4"/>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -1946,9 +2115,6 @@
       <c r="U13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="V13" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W13" s="2" t="s">
         <v>6</v>
       </c>
@@ -1956,7 +2122,7 @@
         <v>6</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>7</v>
@@ -1964,13 +2130,18 @@
       <c r="AA13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB13" s="4"/>
-      <c r="AD13" s="4"/>
+      <c r="AB13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
-      <c r="AH13" s="4"/>
-    </row>
-    <row r="14" spans="1:35" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AG13" s="4"/>
+      <c r="AI13" s="4"/>
+    </row>
+    <row r="14" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2020,9 +2191,6 @@
       <c r="U14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="V14" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W14" s="2" t="s">
         <v>6</v>
       </c>
@@ -2030,7 +2198,7 @@
         <v>6</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>7</v>
@@ -2038,13 +2206,18 @@
       <c r="AA14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB14" s="4"/>
-      <c r="AD14" s="4"/>
+      <c r="AB14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
-      <c r="AH14" s="4"/>
-    </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AG14" s="4"/>
+      <c r="AI14" s="4"/>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2091,9 +2264,6 @@
       <c r="U15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="V15" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W15" s="2" t="s">
         <v>6</v>
       </c>
@@ -2101,7 +2271,7 @@
         <v>6</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z15" s="2" t="s">
         <v>7</v>
@@ -2109,13 +2279,18 @@
       <c r="AA15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB15" s="4"/>
-      <c r="AD15" s="4"/>
+      <c r="AB15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC15" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
-      <c r="AH15" s="4"/>
-    </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AG15" s="4"/>
+      <c r="AI15" s="4"/>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2163,10 +2338,10 @@
         <v>6</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16" s="2" t="s">
         <v>7</v>
@@ -2180,13 +2355,18 @@
       <c r="AA16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB16" s="4"/>
-      <c r="AD16" s="4"/>
+      <c r="AB16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC16" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
-      <c r="AH16" s="4"/>
-    </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG16" s="4"/>
+      <c r="AI16" s="4"/>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2234,10 +2414,10 @@
         <v>6</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X17" s="2" t="s">
         <v>7</v>
@@ -2251,13 +2431,18 @@
       <c r="AA17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB17" s="4"/>
-      <c r="AD17" s="4"/>
+      <c r="AB17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC17" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
-      <c r="AH17" s="4"/>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG17" s="4"/>
+      <c r="AI17" s="4"/>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2305,10 +2490,10 @@
         <v>6</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>6</v>
+        <v>163</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>7</v>
@@ -2322,13 +2507,18 @@
       <c r="AA18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB18" s="4"/>
-      <c r="AD18" s="4"/>
+      <c r="AB18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
-      <c r="AH18" s="4"/>
-    </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG18" s="4"/>
+      <c r="AI18" s="4"/>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2377,17 +2567,14 @@
       <c r="U19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="V19" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="W19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z19" s="2" t="s">
         <v>7</v>
@@ -2395,12 +2582,18 @@
       <c r="AA19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD19" s="4"/>
+      <c r="AB19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC19" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="AE19" s="4"/>
       <c r="AF19" s="4"/>
-      <c r="AH19" s="4"/>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG19" s="4"/>
+      <c r="AI19" s="4"/>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -2446,17 +2639,14 @@
       <c r="U20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="V20" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="W20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>7</v>
@@ -2464,12 +2654,18 @@
       <c r="AA20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD20" s="4"/>
+      <c r="AB20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC20" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="AE20" s="4"/>
       <c r="AF20" s="4"/>
-      <c r="AH20" s="4"/>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG20" s="4"/>
+      <c r="AI20" s="4"/>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -2518,17 +2714,14 @@
       <c r="U21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="V21" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W21" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z21" s="2" t="s">
         <v>7</v>
@@ -2536,12 +2729,18 @@
       <c r="AA21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD21" s="4"/>
+      <c r="AB21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC21" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="AE21" s="4"/>
       <c r="AF21" s="4"/>
-      <c r="AH21" s="4"/>
-    </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG21" s="4"/>
+      <c r="AI21" s="4"/>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -2590,9 +2789,6 @@
       <c r="U22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="V22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W22" s="2" t="s">
         <v>6</v>
       </c>
@@ -2600,7 +2796,7 @@
         <v>6</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>7</v>
@@ -2608,12 +2804,18 @@
       <c r="AA22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD22" s="4"/>
+      <c r="AB22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC22" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="AE22" s="4"/>
       <c r="AF22" s="4"/>
-      <c r="AH22" s="4"/>
-    </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG22" s="4"/>
+      <c r="AI22" s="4"/>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -2662,9 +2864,6 @@
       <c r="U23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="V23" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W23" s="2" t="s">
         <v>6</v>
       </c>
@@ -2672,7 +2871,7 @@
         <v>6</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z23" s="2" t="s">
         <v>7</v>
@@ -2680,12 +2879,18 @@
       <c r="AA23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD23" s="4"/>
+      <c r="AB23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC23" s="2" t="s">
+        <v>146</v>
+      </c>
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
-      <c r="AH23" s="4"/>
-    </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG23" s="4"/>
+      <c r="AI23" s="4"/>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -2734,9 +2939,6 @@
       <c r="U24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="V24" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W24" s="2" t="s">
         <v>6</v>
       </c>
@@ -2744,7 +2946,7 @@
         <v>6</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>7</v>
@@ -2752,12 +2954,18 @@
       <c r="AA24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD24" s="4"/>
+      <c r="AB24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC24" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="AE24" s="4"/>
       <c r="AF24" s="4"/>
-      <c r="AH24" s="4"/>
-    </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG24" s="4"/>
+      <c r="AI24" s="4"/>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -2806,9 +3014,6 @@
       <c r="U25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="V25" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W25" s="2" t="s">
         <v>6</v>
       </c>
@@ -2816,7 +3021,7 @@
         <v>6</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z25" s="2" t="s">
         <v>7</v>
@@ -2824,12 +3029,18 @@
       <c r="AA25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD25" s="4"/>
+      <c r="AB25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC25" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="AE25" s="4"/>
       <c r="AF25" s="4"/>
-      <c r="AH25" s="4"/>
-    </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG25" s="4"/>
+      <c r="AI25" s="4"/>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -2876,9 +3087,6 @@
       <c r="U26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="V26" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="W26" s="2" t="s">
         <v>6</v>
       </c>
@@ -2886,20 +3094,26 @@
         <v>6</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD26" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="AB26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC26" s="2" t="s">
+        <v>150</v>
+      </c>
       <c r="AE26" s="4"/>
       <c r="AF26" s="4"/>
-      <c r="AH26" s="4"/>
-    </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG26" s="4"/>
+      <c r="AI26" s="4"/>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -2943,7 +3157,7 @@
         <v>6</v>
       </c>
       <c r="V27" s="2" t="s">
-        <v>6</v>
+        <v>152</v>
       </c>
       <c r="W27" s="2" t="s">
         <v>6</v>
@@ -2952,20 +3166,26 @@
         <v>6</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z27" s="2" t="s">
         <v>7</v>
       </c>
       <c r="AA27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD27" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="AB27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC27" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
-      <c r="AH27" s="4"/>
-    </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG27" s="4"/>
+      <c r="AI27" s="4"/>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>129</v>
       </c>
@@ -3014,13 +3234,13 @@
         <v>6</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>6</v>
+        <v>153</v>
       </c>
       <c r="W28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y28" s="2" t="s">
         <v>7</v>
@@ -3031,12 +3251,18 @@
       <c r="AA28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AD28" s="4"/>
+      <c r="AB28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC28" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
-      <c r="AH28" s="4"/>
-    </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG28" s="4"/>
+      <c r="AI28" s="4"/>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3082,13 +3308,13 @@
         <v>6</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="W29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y29" s="2" t="s">
         <v>7</v>
@@ -3099,13 +3325,18 @@
       <c r="AA29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB29" s="4"/>
-      <c r="AD29" s="4"/>
+      <c r="AB29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC29" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="AE29" s="4"/>
       <c r="AF29" s="4"/>
-      <c r="AH29" s="4"/>
-    </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG29" s="4"/>
+      <c r="AI29" s="4"/>
+    </row>
+    <row r="30" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3149,13 +3380,13 @@
         <v>6</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>6</v>
+        <v>155</v>
       </c>
       <c r="W30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y30" s="2" t="s">
         <v>7</v>
@@ -3164,15 +3395,20 @@
         <v>7</v>
       </c>
       <c r="AA30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB30" s="4"/>
-      <c r="AD30" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="AB30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC30" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="AE30" s="4"/>
       <c r="AF30" s="4"/>
-      <c r="AH30" s="4"/>
-    </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG30" s="4"/>
+      <c r="AI30" s="4"/>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -3215,13 +3451,13 @@
         <v>6</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>6</v>
+        <v>156</v>
       </c>
       <c r="W31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y31" s="2" t="s">
         <v>7</v>
@@ -3232,13 +3468,18 @@
       <c r="AA31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB31" s="4"/>
-      <c r="AD31" s="4"/>
+      <c r="AB31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC31" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="AE31" s="4"/>
       <c r="AF31" s="4"/>
-      <c r="AH31" s="4"/>
-    </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.15">
+      <c r="AG31" s="4"/>
+      <c r="AI31" s="4"/>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.15">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -3281,13 +3522,13 @@
         <v>6</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>6</v>
+        <v>157</v>
       </c>
       <c r="W32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y32" s="2" t="s">
         <v>7</v>
@@ -3298,13 +3539,18 @@
       <c r="AA32" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AB32" s="4"/>
-      <c r="AD32" s="4"/>
+      <c r="AB32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC32" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="AE32" s="4"/>
       <c r="AF32" s="4"/>
-      <c r="AH32" s="4"/>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG32" s="4"/>
+      <c r="AI32" s="4"/>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -3318,13 +3564,12 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
-      <c r="AB33" s="4"/>
-      <c r="AD33" s="4"/>
       <c r="AE33" s="4"/>
       <c r="AF33" s="4"/>
-      <c r="AH33" s="4"/>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG33" s="4"/>
+      <c r="AI33" s="4"/>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -3338,13 +3583,12 @@
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
-      <c r="AB34" s="4"/>
-      <c r="AD34" s="4"/>
       <c r="AE34" s="4"/>
       <c r="AF34" s="4"/>
-      <c r="AH34" s="4"/>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG34" s="4"/>
+      <c r="AI34" s="4"/>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -3358,13 +3602,12 @@
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
-      <c r="AB35" s="4"/>
-      <c r="AD35" s="4"/>
       <c r="AE35" s="4"/>
       <c r="AF35" s="4"/>
-      <c r="AH35" s="4"/>
-    </row>
-    <row r="36" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG35" s="4"/>
+      <c r="AI35" s="4"/>
+    </row>
+    <row r="36" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -3378,13 +3621,12 @@
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
-      <c r="AB36" s="4"/>
-      <c r="AD36" s="4"/>
       <c r="AE36" s="4"/>
       <c r="AF36" s="4"/>
-      <c r="AH36" s="4"/>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG36" s="4"/>
+      <c r="AI36" s="4"/>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -3398,13 +3640,12 @@
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
-      <c r="AB37" s="4"/>
-      <c r="AD37" s="4"/>
       <c r="AE37" s="4"/>
       <c r="AF37" s="4"/>
-      <c r="AH37" s="4"/>
-    </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG37" s="4"/>
+      <c r="AI37" s="4"/>
+    </row>
+    <row r="38" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -3418,13 +3659,12 @@
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
-      <c r="AB38" s="4"/>
-      <c r="AD38" s="4"/>
       <c r="AE38" s="4"/>
       <c r="AF38" s="4"/>
-      <c r="AH38" s="4"/>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG38" s="4"/>
+      <c r="AI38" s="4"/>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3438,13 +3678,12 @@
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
-      <c r="AB39" s="4"/>
-      <c r="AD39" s="4"/>
       <c r="AE39" s="4"/>
       <c r="AF39" s="4"/>
-      <c r="AH39" s="4"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG39" s="4"/>
+      <c r="AI39" s="4"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3458,12 +3697,12 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="AD40" s="4"/>
       <c r="AE40" s="4"/>
       <c r="AF40" s="4"/>
-      <c r="AH40" s="4"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG40" s="4"/>
+      <c r="AI40" s="4"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3477,12 +3716,12 @@
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
-      <c r="AD41" s="4"/>
       <c r="AE41" s="4"/>
       <c r="AF41" s="4"/>
-      <c r="AH41" s="4"/>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG41" s="4"/>
+      <c r="AI41" s="4"/>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -3496,12 +3735,12 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="AD42" s="4"/>
       <c r="AE42" s="4"/>
       <c r="AF42" s="4"/>
-      <c r="AH42" s="4"/>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG42" s="4"/>
+      <c r="AI42" s="4"/>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -3515,12 +3754,12 @@
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
-      <c r="AD43" s="4"/>
       <c r="AE43" s="4"/>
       <c r="AF43" s="4"/>
-      <c r="AH43" s="4"/>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG43" s="4"/>
+      <c r="AI43" s="4"/>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -3534,37 +3773,37 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="AD44" s="4"/>
       <c r="AE44" s="4"/>
       <c r="AF44" s="4"/>
-      <c r="AH44" s="4"/>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG44" s="4"/>
+      <c r="AI44" s="4"/>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="AD45" s="4"/>
       <c r="AE45" s="4"/>
       <c r="AF45" s="4"/>
-      <c r="AH45" s="4"/>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AG45" s="4"/>
+      <c r="AI45" s="4"/>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
-      <c r="AD46" s="4"/>
-      <c r="AF46" s="4"/>
-      <c r="AH46" s="4"/>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.15">
+      <c r="AE46" s="4"/>
+      <c r="AG46" s="4"/>
+      <c r="AI46" s="4"/>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.15">
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A8CDEB-F0AC-4472-9E97-71B000CF7AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD49EEB-2F6E-4A86-83D7-56934D6E6C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="36" r:id="rId1"/>
@@ -603,10 +603,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>91</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>92</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -636,6 +632,10 @@
   </si>
   <si>
     <t>67</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1509,7 +1509,7 @@
         <v>6</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>6</v>
@@ -1657,7 +1657,7 @@
         <v>6</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>6</v>
@@ -1733,7 +1733,7 @@
         <v>6</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>6</v>
@@ -1812,7 +1812,7 @@
         <v>6</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>6</v>
@@ -1888,7 +1888,7 @@
         <v>6</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>6</v>
@@ -1964,7 +1964,7 @@
         <v>6</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>6</v>
@@ -2040,7 +2040,7 @@
         <v>6</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>6</v>
@@ -2338,7 +2338,7 @@
         <v>6</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>6</v>
@@ -2414,7 +2414,7 @@
         <v>6</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="W17" s="2" t="s">
         <v>6</v>
@@ -2490,7 +2490,7 @@
         <v>6</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="W18" s="2" t="s">
         <v>6</v>
@@ -3451,7 +3451,7 @@
         <v>6</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="W31" s="2" t="s">
         <v>6</v>
@@ -3522,7 +3522,7 @@
         <v>6</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W32" s="2" t="s">
         <v>6</v>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD49EEB-2F6E-4A86-83D7-56934D6E6C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EDDAD8-03A5-4C7B-B3D3-D9073493307E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -506,10 +506,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{class:"AddBuff",buffId:1,probability:5000,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:1,probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>螺旋突刺</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -636,6 +632,10 @@
   </si>
   <si>
     <t>29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"AddBuff",buffId:1,probability:1500,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:1,probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1230,10 +1230,10 @@
         <v>41</v>
       </c>
       <c r="AB1" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AC1" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AD1" s="6"/>
       <c r="AE1" s="8"/>
@@ -1346,7 +1346,7 @@
         <v>46</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="W3" s="7" t="s">
         <v>38</v>
@@ -1367,7 +1367,7 @@
         <v>99</v>
       </c>
       <c r="AC3" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD3" s="7"/>
       <c r="AE3" s="7"/>
@@ -1509,7 +1509,7 @@
         <v>6</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>6</v>
@@ -1530,7 +1530,7 @@
         <v>7</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
@@ -1599,7 +1599,7 @@
         <v>7</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
@@ -1657,7 +1657,7 @@
         <v>6</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>6</v>
@@ -1678,7 +1678,7 @@
         <v>7</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
@@ -1690,7 +1690,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>42</v>
@@ -1727,13 +1727,13 @@
         <v>7</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>6</v>
@@ -1812,7 +1812,7 @@
         <v>6</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>6</v>
@@ -1833,7 +1833,7 @@
         <v>7</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
@@ -1888,7 +1888,7 @@
         <v>6</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>6</v>
@@ -1964,7 +1964,7 @@
         <v>6</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>6</v>
@@ -1985,7 +1985,7 @@
         <v>7</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
@@ -2040,7 +2040,7 @@
         <v>6</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>6</v>
@@ -2061,7 +2061,7 @@
         <v>7</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
@@ -2134,7 +2134,7 @@
         <v>7</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
@@ -2210,7 +2210,7 @@
         <v>7</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
@@ -2283,7 +2283,7 @@
         <v>7</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
@@ -2338,7 +2338,7 @@
         <v>6</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>6</v>
@@ -2359,7 +2359,7 @@
         <v>7</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
@@ -2414,7 +2414,7 @@
         <v>6</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="W17" s="2" t="s">
         <v>6</v>
@@ -2435,7 +2435,7 @@
         <v>7</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
@@ -2490,7 +2490,7 @@
         <v>6</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="W18" s="2" t="s">
         <v>6</v>
@@ -2511,7 +2511,7 @@
         <v>7</v>
       </c>
       <c r="AC18" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
@@ -2586,7 +2586,7 @@
         <v>7</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AE19" s="4"/>
       <c r="AF19" s="4"/>
@@ -2658,7 +2658,7 @@
         <v>7</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AE20" s="4"/>
       <c r="AF20" s="4"/>
@@ -2733,7 +2733,7 @@
         <v>7</v>
       </c>
       <c r="AC21" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AE21" s="4"/>
       <c r="AF21" s="4"/>
@@ -2808,7 +2808,7 @@
         <v>7</v>
       </c>
       <c r="AC22" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AE22" s="4"/>
       <c r="AF22" s="4"/>
@@ -2883,7 +2883,7 @@
         <v>7</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
@@ -2958,7 +2958,7 @@
         <v>7</v>
       </c>
       <c r="AC24" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AE24" s="4"/>
       <c r="AF24" s="4"/>
@@ -3033,7 +3033,7 @@
         <v>7</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AE25" s="4"/>
       <c r="AF25" s="4"/>
@@ -3106,7 +3106,7 @@
         <v>7</v>
       </c>
       <c r="AC26" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AE26" s="4"/>
       <c r="AF26" s="4"/>
@@ -3157,7 +3157,7 @@
         <v>6</v>
       </c>
       <c r="V27" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="W27" s="2" t="s">
         <v>6</v>
@@ -3178,7 +3178,7 @@
         <v>6</v>
       </c>
       <c r="AC27" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
@@ -3218,7 +3218,7 @@
         <v>106</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N28" s="4">
         <v>0</v>
@@ -3234,7 +3234,7 @@
         <v>6</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="W28" s="2" t="s">
         <v>6</v>
@@ -3255,7 +3255,7 @@
         <v>7</v>
       </c>
       <c r="AC28" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
@@ -3292,7 +3292,7 @@
         <v>107</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N29" s="4">
         <v>0</v>
@@ -3308,7 +3308,7 @@
         <v>6</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="W29" s="2" t="s">
         <v>6</v>
@@ -3329,7 +3329,7 @@
         <v>7</v>
       </c>
       <c r="AC29" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AE29" s="4"/>
       <c r="AF29" s="4"/>
@@ -3364,7 +3364,7 @@
         <v>108</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N30" s="4">
         <v>0</v>
@@ -3380,7 +3380,7 @@
         <v>6</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="W30" s="2" t="s">
         <v>6</v>
@@ -3401,7 +3401,7 @@
         <v>6</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AE30" s="4"/>
       <c r="AF30" s="4"/>
@@ -3451,7 +3451,7 @@
         <v>6</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W31" s="2" t="s">
         <v>6</v>
@@ -3472,7 +3472,7 @@
         <v>7</v>
       </c>
       <c r="AC31" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AE31" s="4"/>
       <c r="AF31" s="4"/>
@@ -3522,7 +3522,7 @@
         <v>6</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="W32" s="2" t="s">
         <v>6</v>
@@ -3543,7 +3543,7 @@
         <v>7</v>
       </c>
       <c r="AC32" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AE32" s="4"/>
       <c r="AF32" s="4"/>

--- a/Data/Export/Common/Skill_技能.xlsx
+++ b/Data/Export/Common/Skill_技能.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EDDAD8-03A5-4C7B-B3D3-D9073493307E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF7F636-C03E-4007-8F70-462FEFF6CB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="169">
   <si>
     <t>备注:</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -637,6 +637,19 @@
   <si>
     <t>[{class:"AddBuff",buffId:1,probability:1500,values:[1,2], weight:[70,30],condition:{class:"SkillIsCritical",result:0}},{class:"AddBuff",buffId:1,probability:10000,values:[2,3], weight:[70,30],condition:{class:"SkillIsCritical",result:1}}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spellConditionMethod</t>
+  </si>
+  <si>
+    <t>释放检查额外条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckFire</t>
+  </si>
+  <si>
+    <t>CheckDebuffTroop</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
-  <dimension ref="A1:AJ69"/>
+  <dimension ref="A1:AK69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.375" style="2" bestFit="1" customWidth="1"/>
@@ -1142,18 +1155,19 @@
     <col min="18" max="18" width="255.625" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17" style="2" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.75" style="2" customWidth="1"/>
-    <col min="22" max="22" width="18.25" style="2" customWidth="1"/>
+    <col min="21" max="21" width="18.25" style="2" customWidth="1"/>
+    <col min="22" max="22" width="19.75" style="2" customWidth="1"/>
     <col min="23" max="23" width="20.75" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="17" style="2" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="22" style="2" bestFit="1" customWidth="1"/>
     <col min="26" max="28" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.25" style="2" customWidth="1"/>
-    <col min="30" max="30" width="70.5" style="2" customWidth="1"/>
-    <col min="31" max="16384" width="9" style="2"/>
+    <col min="29" max="29" width="25.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.25" style="2" customWidth="1"/>
+    <col min="31" max="31" width="70.5" style="2" customWidth="1"/>
+    <col min="32" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:37" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="12" t="s">
         <v>9</v>
@@ -1210,10 +1224,10 @@
       <c r="T1" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="16"/>
+      <c r="V1" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="V1" s="16"/>
       <c r="W1" s="12" t="s">
         <v>15</v>
       </c>
@@ -1232,18 +1246,21 @@
       <c r="AB1" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="AC1" s="16" t="s">
+      <c r="AC1" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="AD1" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="8"/>
-      <c r="AF1" s="6"/>
-      <c r="AG1" s="8"/>
-      <c r="AH1" s="6"/>
-      <c r="AI1" s="8"/>
-      <c r="AJ1" s="6"/>
-    </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="6"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="6"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="6"/>
+    </row>
+    <row r="2" spans="1:37" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1266,24 +1283,25 @@
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="4"/>
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="2"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="3"/>
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
-    </row>
-    <row r="3" spans="1:36" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AK2" s="2"/>
+    </row>
+    <row r="3" spans="1:37" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1343,10 +1361,10 @@
         <v>66</v>
       </c>
       <c r="U3" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="V3" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>150</v>
       </c>
       <c r="W3" s="7" t="s">
         <v>38</v>
@@ -1367,17 +1385,20 @@
         <v>99</v>
       </c>
       <c r="AC3" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AD3" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="AD3" s="7"/>
       <c r="AE3" s="7"/>
       <c r="AF3" s="7"/>
       <c r="AG3" s="7"/>
       <c r="AH3" s="7"/>
       <c r="AI3" s="7"/>
       <c r="AJ3" s="7"/>
-    </row>
-    <row r="4" spans="1:36" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AK3" s="7"/>
+    </row>
+    <row r="4" spans="1:37" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1438,11 +1459,11 @@
       <c r="T4" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="U4" s="13" t="s">
+      <c r="U4" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="V4" s="13" t="s">
         <v>8</v>
-      </c>
-      <c r="V4" s="14" t="s">
-        <v>65</v>
       </c>
       <c r="W4" s="13" t="s">
         <v>8</v>
@@ -1462,11 +1483,14 @@
       <c r="AB4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AC4" s="14" t="s">
+      <c r="AC4" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD4" s="14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1506,10 +1530,10 @@
         <v>7</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>6</v>
+        <v>156</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>156</v>
+        <v>6</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>6</v>
@@ -1529,15 +1553,15 @@
       <c r="AB5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC5" s="2" t="s">
+      <c r="AD5" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="4"/>
-      <c r="AI5" s="4"/>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AH5" s="4"/>
+      <c r="AJ5" s="4"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1577,7 +1601,7 @@
       <c r="P6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="V6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="W6" s="2" t="s">
@@ -1598,15 +1622,15 @@
       <c r="AB6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC6" s="2" t="s">
+      <c r="AD6" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="AE6" s="4"/>
       <c r="AF6" s="4"/>
       <c r="AG6" s="4"/>
-      <c r="AI6" s="4"/>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AH6" s="4"/>
+      <c r="AJ6" s="4"/>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1654,10 +1678,10 @@
         <v>70</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>162</v>
+        <v>6</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>6</v>
@@ -1677,15 +1701,15 @@
       <c r="AB7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AD7" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="AE7" s="4"/>
       <c r="AF7" s="4"/>
       <c r="AG7" s="4"/>
-      <c r="AI7" s="4"/>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AH7" s="4"/>
+      <c r="AJ7" s="4"/>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1730,10 +1754,10 @@
         <v>164</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>162</v>
+        <v>6</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>6</v>
@@ -1753,15 +1777,15 @@
       <c r="AB8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC8" s="2">
+      <c r="AD8" s="2">
         <v>2838</v>
       </c>
-      <c r="AE8" s="4"/>
       <c r="AF8" s="4"/>
       <c r="AG8" s="4"/>
-      <c r="AI8" s="4"/>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AH8" s="4"/>
+      <c r="AJ8" s="4"/>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -1809,10 +1833,10 @@
         <v>71</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>162</v>
+        <v>6</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>6</v>
@@ -1832,15 +1856,15 @@
       <c r="AB9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC9" s="2" t="s">
+      <c r="AD9" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="4"/>
-      <c r="AI9" s="4"/>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AH9" s="4"/>
+      <c r="AJ9" s="4"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -1885,10 +1909,10 @@
         <v>74</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>6</v>
+        <v>157</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>157</v>
+        <v>6</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>6</v>
@@ -1908,15 +1932,15 @@
       <c r="AB10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC10" s="2">
+      <c r="AD10" s="2">
         <v>2866</v>
       </c>
-      <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="4"/>
-      <c r="AI10" s="4"/>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AH10" s="4"/>
+      <c r="AJ10" s="4"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -1961,10 +1985,10 @@
         <v>60</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>6</v>
@@ -1984,15 +2008,15 @@
       <c r="AB11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC11" s="2" t="s">
+      <c r="AD11" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="4"/>
-      <c r="AI11" s="4"/>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AH11" s="4"/>
+      <c r="AJ11" s="4"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2037,10 +2061,10 @@
         <v>59</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>6</v>
+        <v>159</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>159</v>
+        <v>6</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>6</v>
@@ -2060,15 +2084,15 @@
       <c r="AB12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC12" s="2" t="s">
+      <c r="AD12" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="4"/>
-      <c r="AI12" s="4"/>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AH12" s="4"/>
+      <c r="AJ12" s="4"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2112,7 +2136,7 @@
       <c r="R13" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="U13" s="2" t="s">
+      <c r="V13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="W13" s="2" t="s">
@@ -2133,15 +2157,15 @@
       <c r="AB13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC13" s="2" t="s">
+      <c r="AD13" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="4"/>
-      <c r="AI13" s="4"/>
-    </row>
-    <row r="14" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AH13" s="4"/>
+      <c r="AJ13" s="4"/>
+    </row>
+    <row r="14" spans="1:37" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2188,7 +2212,7 @@
       <c r="Q14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="U14" s="2" t="s">
+      <c r="V14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="W14" s="2" t="s">
@@ -2209,15 +2233,15 @@
       <c r="AB14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC14" s="2" t="s">
+      <c r="AD14" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="4"/>
-      <c r="AI14" s="4"/>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AH14" s="4"/>
+      <c r="AJ14" s="4"/>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2261,7 +2285,7 @@
       <c r="Q15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="U15" s="2" t="s">
+      <c r="V15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="W15" s="2" t="s">
@@ -2282,15 +2306,15 @@
       <c r="AB15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC15" s="2" t="s">
+      <c r="AD15" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="4"/>
-      <c r="AI15" s="4"/>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.15">
+      <c r="AH15" s="4"/>
+      <c r="AJ15" s="4"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2335,10 +2359,10 @@
         <v>75</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>6</v>
+        <v>160</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>160</v>
+        <v>6</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>6</v>
@@ -2358,15 +2382,15 @@
       <c r="AB16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC16" s="2" t="s">
+      <c r="AD16" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="4"/>
-      <c r="AI16" s="4"/>
-    </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH16" s="4"/>
+      <c r="AJ16" s="4"/>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -2411,10 +2435,10 @@
         <v>79</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>6</v>
+        <v>160</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>160</v>
+        <v>6</v>
       </c>
       <c r="W17" s="2" t="s">
         <v>6</v>
@@ -2434,15 +2458,15 @@
       <c r="AB17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC17" s="2" t="s">
+      <c r="AD17" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="4"/>
-      <c r="AI17" s="4"/>
-    </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH17" s="4"/>
+      <c r="AJ17" s="4"/>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -2487,10 +2511,10 @@
         <v>76</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>6</v>
+        <v>161</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>161</v>
+        <v>6</v>
       </c>
       <c r="W18" s="2" t="s">
         <v>6</v>
@@ -2510,15 +2534,15 @@
       <c r="AB18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC18" s="2" t="s">
+      <c r="AD18" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="4"/>
-      <c r="AI18" s="4"/>
-    </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH18" s="4"/>
+      <c r="AJ18" s="4"/>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -2564,7 +2588,7 @@
       <c r="R19" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="U19" s="2" t="s">
+      <c r="V19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="W19" s="2" t="s">
@@ -2585,15 +2609,15 @@
       <c r="AB19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC19" s="2" t="s">
+      <c r="AD19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AE19" s="4"/>
       <c r="AF19" s="4"/>
       <c r="AG19" s="4"/>
-      <c r="AI19" s="4"/>
-    </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH19" s="4"/>
+      <c r="AJ19" s="4"/>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -2636,7 +2660,7 @@
       <c r="P20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="U20" s="2" t="s">
+      <c r="V20" s="2" t="s">
         <v>7</v>
       </c>
       <c r="W20" s="2" t="s">
@@ -2657,15 +2681,15 @@
       <c r="AB20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC20" s="2" t="s">
+      <c r="AD20" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="AE20" s="4"/>
       <c r="AF20" s="4"/>
       <c r="AG20" s="4"/>
-      <c r="AI20" s="4"/>
-    </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH20" s="4"/>
+      <c r="AJ20" s="4"/>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -2711,7 +2735,7 @@
       <c r="R21" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="U21" s="2" t="s">
+      <c r="V21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="W21" s="2" t="s">
@@ -2732,15 +2756,15 @@
       <c r="AB21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC21" s="2" t="s">
+      <c r="AD21" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="AE21" s="4"/>
       <c r="AF21" s="4"/>
       <c r="AG21" s="4"/>
-      <c r="AI21" s="4"/>
-    </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH21" s="4"/>
+      <c r="AJ21" s="4"/>
+    </row>
+    <row r="22" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -2786,7 +2810,7 @@
       <c r="Q22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="U22" s="2" t="s">
+      <c r="V22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="W22" s="2" t="s">
@@ -2807,15 +2831,15 @@
       <c r="AB22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC22" s="2" t="s">
+      <c r="AD22" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="AE22" s="4"/>
       <c r="AF22" s="4"/>
       <c r="AG22" s="4"/>
-      <c r="AI22" s="4"/>
-    </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH22" s="4"/>
+      <c r="AJ22" s="4"/>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -2861,7 +2885,7 @@
       <c r="R23" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="U23" s="2" t="s">
+      <c r="V23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="W23" s="2" t="s">
@@ -2882,15 +2906,15 @@
       <c r="AB23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC23" s="2" t="s">
+      <c r="AD23" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
       <c r="AG23" s="4"/>
-      <c r="AI23" s="4"/>
-    </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH23" s="4"/>
+      <c r="AJ23" s="4"/>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -2936,7 +2960,7 @@
       <c r="S24" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="U24" s="2" t="s">
+      <c r="V24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="W24" s="2" t="s">
@@ -2957,15 +2981,15 @@
       <c r="AB24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC24" s="2" t="s">
+      <c r="AD24" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="AE24" s="4"/>
       <c r="AF24" s="4"/>
       <c r="AG24" s="4"/>
-      <c r="AI24" s="4"/>
-    </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH24" s="4"/>
+      <c r="AJ24" s="4"/>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -3011,7 +3035,7 @@
       <c r="Q25" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="U25" s="2" t="s">
+      <c r="V25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="W25" s="2" t="s">
@@ -3032,15 +3056,15 @@
       <c r="AB25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC25" s="2" t="s">
+      <c r="AD25" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="AE25" s="4"/>
       <c r="AF25" s="4"/>
       <c r="AG25" s="4"/>
-      <c r="AI25" s="4"/>
-    </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH25" s="4"/>
+      <c r="AJ25" s="4"/>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -3084,7 +3108,7 @@
       <c r="R26" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="U26" s="2" t="s">
+      <c r="V26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="W26" s="2" t="s">
@@ -3105,15 +3129,15 @@
       <c r="AB26" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC26" s="2" t="s">
+      <c r="AD26" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="AE26" s="4"/>
       <c r="AF26" s="4"/>
       <c r="AG26" s="4"/>
-      <c r="AI26" s="4"/>
-    </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH26" s="4"/>
+      <c r="AJ26" s="4"/>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -3154,10 +3178,10 @@
         <v>118</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>6</v>
+        <v>151</v>
       </c>
       <c r="V27" s="2" t="s">
-        <v>151</v>
+        <v>6</v>
       </c>
       <c r="W27" s="2" t="s">
         <v>6</v>
@@ -3172,20 +3196,23 @@
         <v>7</v>
       </c>
       <c r="AA27" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AC27" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="AD27" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
       <c r="AG27" s="4"/>
-      <c r="AI27" s="4"/>
-    </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH27" s="4"/>
+      <c r="AJ27" s="4"/>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>129</v>
       </c>
@@ -3231,10 +3258,10 @@
         <v>119</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>6</v>
+        <v>152</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>152</v>
+        <v>6</v>
       </c>
       <c r="W28" s="2" t="s">
         <v>6</v>
@@ -3254,15 +3281,15 @@
       <c r="AB28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC28" s="2" t="s">
+      <c r="AD28" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
       <c r="AG28" s="4"/>
-      <c r="AI28" s="4"/>
-    </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH28" s="4"/>
+      <c r="AJ28" s="4"/>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3305,10 +3332,10 @@
         <v>120</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>6</v>
+        <v>153</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>153</v>
+        <v>6</v>
       </c>
       <c r="W29" s="2" t="s">
         <v>6</v>
@@ -3328,15 +3355,15 @@
       <c r="AB29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC29" s="2" t="s">
+      <c r="AD29" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="AE29" s="4"/>
       <c r="AF29" s="4"/>
       <c r="AG29" s="4"/>
-      <c r="AI29" s="4"/>
-    </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH29" s="4"/>
+      <c r="AJ29" s="4"/>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -3377,10 +3404,10 @@
         <v>122</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="W30" s="2" t="s">
         <v>6</v>
@@ -3392,7 +3419,7 @@
         <v>7</v>
       </c>
       <c r="Z30" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA30" s="2" t="s">
         <v>7</v>
@@ -3401,14 +3428,17 @@
         <v>6</v>
       </c>
       <c r="AC30" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="AD30" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="AE30" s="4"/>
       <c r="AF30" s="4"/>
       <c r="AG30" s="4"/>
-      <c r="AI30" s="4"/>
-    </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH30" s="4"/>
+      <c r="AJ30" s="4"/>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -3448,10 +3478,10 @@
         <v>6</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>6</v>
+        <v>163</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>163</v>
+        <v>6</v>
       </c>
       <c r="W31" s="2" t="s">
         <v>6</v>
@@ -3471,15 +3501,15 @@
       <c r="AB31" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC31" s="2" t="s">
+      <c r="AD31" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="AE31" s="4"/>
       <c r="AF31" s="4"/>
       <c r="AG31" s="4"/>
-      <c r="AI31" s="4"/>
-    </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.15">
+      <c r="AH31" s="4"/>
+      <c r="AJ31" s="4"/>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.15">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -3519,10 +3549,10 @@
         <v>6</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>6</v>
+        <v>155</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>155</v>
+        <v>6</v>
       </c>
       <c r="W32" s="2" t="s">
         <v>6</v>
@@ -3542,15 +3572,15 @@
       <c r="AB32" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AC32" s="2" t="s">
+      <c r="AD32" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="AE32" s="4"/>
       <c r="AF32" s="4"/>
       <c r="AG32" s="4"/>
-      <c r="AI32" s="4"/>
-    </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH32" s="4"/>
+      <c r="AJ32" s="4"/>
+    </row>
+    <row r="33" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -3564,12 +3594,12 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
-      <c r="AE33" s="4"/>
       <c r="AF33" s="4"/>
       <c r="AG33" s="4"/>
-      <c r="AI33" s="4"/>
-    </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH33" s="4"/>
+      <c r="AJ33" s="4"/>
+    </row>
+    <row r="34" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -3583,12 +3613,12 @@
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
-      <c r="AE34" s="4"/>
       <c r="AF34" s="4"/>
       <c r="AG34" s="4"/>
-      <c r="AI34" s="4"/>
-    </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH34" s="4"/>
+      <c r="AJ34" s="4"/>
+    </row>
+    <row r="35" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -3602,12 +3632,12 @@
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
-      <c r="AE35" s="4"/>
       <c r="AF35" s="4"/>
       <c r="AG35" s="4"/>
-      <c r="AI35" s="4"/>
-    </row>
-    <row r="36" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH35" s="4"/>
+      <c r="AJ35" s="4"/>
+    </row>
+    <row r="36" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -3621,12 +3651,12 @@
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
-      <c r="AE36" s="4"/>
       <c r="AF36" s="4"/>
       <c r="AG36" s="4"/>
-      <c r="AI36" s="4"/>
-    </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH36" s="4"/>
+      <c r="AJ36" s="4"/>
+    </row>
+    <row r="37" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -3640,12 +3670,12 @@
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
-      <c r="AE37" s="4"/>
       <c r="AF37" s="4"/>
       <c r="AG37" s="4"/>
-      <c r="AI37" s="4"/>
-    </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH37" s="4"/>
+      <c r="AJ37" s="4"/>
+    </row>
+    <row r="38" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -3659,12 +3689,12 @@
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
-      <c r="AE38" s="4"/>
       <c r="AF38" s="4"/>
       <c r="AG38" s="4"/>
-      <c r="AI38" s="4"/>
-    </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH38" s="4"/>
+      <c r="AJ38" s="4"/>
+    </row>
+    <row r="39" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3678,12 +3708,12 @@
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
-      <c r="AE39" s="4"/>
       <c r="AF39" s="4"/>
       <c r="AG39" s="4"/>
-      <c r="AI39" s="4"/>
-    </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH39" s="4"/>
+      <c r="AJ39" s="4"/>
+    </row>
+    <row r="40" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3697,12 +3727,12 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="AE40" s="4"/>
       <c r="AF40" s="4"/>
       <c r="AG40" s="4"/>
-      <c r="AI40" s="4"/>
-    </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH40" s="4"/>
+      <c r="AJ40" s="4"/>
+    </row>
+    <row r="41" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3716,12 +3746,12 @@
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
-      <c r="AE41" s="4"/>
       <c r="AF41" s="4"/>
       <c r="AG41" s="4"/>
-      <c r="AI41" s="4"/>
-    </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH41" s="4"/>
+      <c r="AJ41" s="4"/>
+    </row>
+    <row r="42" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -3735,12 +3765,12 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="AE42" s="4"/>
       <c r="AF42" s="4"/>
       <c r="AG42" s="4"/>
-      <c r="AI42" s="4"/>
-    </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH42" s="4"/>
+      <c r="AJ42" s="4"/>
+    </row>
+    <row r="43" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -3754,12 +3784,12 @@
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
-      <c r="AE43" s="4"/>
       <c r="AF43" s="4"/>
       <c r="AG43" s="4"/>
-      <c r="AI43" s="4"/>
-    </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH43" s="4"/>
+      <c r="AJ43" s="4"/>
+    </row>
+    <row r="44" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -3773,37 +3803,37 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="AE44" s="4"/>
       <c r="AF44" s="4"/>
       <c r="AG44" s="4"/>
-      <c r="AI44" s="4"/>
-    </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH44" s="4"/>
+      <c r="AJ44" s="4"/>
+    </row>
+    <row r="45" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="AE45" s="4"/>
       <c r="AF45" s="4"/>
       <c r="AG45" s="4"/>
-      <c r="AI45" s="4"/>
-    </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AH45" s="4"/>
+      <c r="AJ45" s="4"/>
+    </row>
+    <row r="46" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
-      <c r="AE46" s="4"/>
-      <c r="AG46" s="4"/>
-      <c r="AI46" s="4"/>
-    </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="AF46" s="4"/>
+      <c r="AH46" s="4"/>
+      <c r="AJ46" s="4"/>
+    </row>
+    <row r="47" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.15">
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
